--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_importance.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_importance.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1565015774302235</v>
+        <v>0.1535059903451239</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1399342130134622</v>
+        <v>0.1380366604696395</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1385997177960469</v>
+        <v>0.1363384666512138</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1336178133538872</v>
+        <v>0.1361030124670234</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1335803656267694</v>
+        <v>0.134526958687736</v>
       </c>
     </row>
     <row r="7">
@@ -528,11 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1307988872404872</v>
+        <v>0.1336886470147768</v>
       </c>
     </row>
     <row r="8">
@@ -543,11 +543,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1301761441994159</v>
+        <v>0.1307381042215675</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03679128133970771</v>
+        <v>0.03706216014291917</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1552906545907209</v>
+        <v>0.1527607816580586</v>
       </c>
     </row>
     <row r="11">
@@ -588,11 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.139949044946875</v>
+        <v>0.1405018202675423</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1391526454473694</v>
+        <v>0.1366408190029702</v>
       </c>
     </row>
     <row r="13">
@@ -618,11 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1354430373449654</v>
+        <v>0.135849975698817</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1335994330183154</v>
+        <v>0.1353843562500654</v>
       </c>
     </row>
     <row r="15">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1321020464894978</v>
+        <v>0.1331573259537452</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1298815375207435</v>
+        <v>0.1298636672183948</v>
       </c>
     </row>
     <row r="17">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03458160064151278</v>
+        <v>0.03584125395040662</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1542284887975553</v>
+        <v>0.1601554881588104</v>
       </c>
     </row>
     <row r="19">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1437346036012838</v>
+        <v>0.1442649486160315</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1412829080633718</v>
+        <v>0.1382853539390956</v>
       </c>
     </row>
     <row r="21">
@@ -738,11 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1324924252483331</v>
+        <v>0.1367019510914014</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1324347336496812</v>
+        <v>0.1332394777243762</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1310611491123007</v>
+        <v>0.1281227948456441</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1293870174478751</v>
+        <v>0.1266021055426002</v>
       </c>
     </row>
     <row r="25">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.03537867407959915</v>
+        <v>0.03262788008204052</v>
       </c>
     </row>
   </sheetData>
